--- a/XBRL-template-MPERS/backup-originals/Company/06-SOCI-NetOfTax.xlsx
+++ b/XBRL-template-MPERS/backup-originals/Company/06-SOCI-NetOfTax.xlsx
@@ -629,10 +629,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Total comprehensive income</t>
-        </is>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>*Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>1*B25+1*B11</f>
+        <v/>
+      </c>
+      <c r="C26">
+        <f>1*C25+1*C11</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -663,11 +671,11 @@
         </is>
       </c>
       <c r="B30">
-        <f>1*B25+1*B28+1*B11+1*B29</f>
+        <f>1*B28+1*B29</f>
         <v/>
       </c>
       <c r="C30">
-        <f>1*C25+1*C28+1*C11+1*C29</f>
+        <f>1*C28+1*C29</f>
         <v/>
       </c>
     </row>
